--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-consent.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-consent.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Consent</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Consent|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -446,7 +446,7 @@
     <t>Consent.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -484,7 +484,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -542,7 +542,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -718,7 +718,7 @@
     <t>同意リソースの4つの予想される使用。 / The four anticipated uses for the Consent Resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-scope</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-scope|4.0.1</t>
   </si>
   <si>
     <t>Consent.category</t>
@@ -733,7 +733,7 @@
     <t>同意声明で見つかった同意のタイプの分類。 / A classification of the type of consents found in a consent statement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-category</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-category|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -751,7 +751,7 @@
     <t>Consent.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(Patient|4.0.1)
 </t>
   </si>
   <si>
@@ -808,7 +808,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
+    <t xml:space="preserve">Reference(Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -837,7 +837,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -854,7 +854,7 @@
   </si>
   <si>
     <t>Attachment
-Reference(Consent|DocumentReference|Contract|QuestionnaireResponse)</t>
+Reference(Consent|4.0.1|DocumentReference|4.0.1|Contract|4.0.1|QuestionnaireResponse|4.0.1)</t>
   </si>
   <si>
     <t>この同意が得られる情報源 / Source from which this consent is taken</t>
@@ -955,7 +955,7 @@
     <t>規制政策の例。 / Regulatory policy examples.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-policy</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-policy|4.0.1</t>
   </si>
   <si>
     <t>Consent.verification</t>
@@ -992,7 +992,7 @@
     <t>Consent.verification.verifiedWith</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1090,13 +1090,13 @@
     <t>同意書対象者が同意の考慮事項にどのように関与しているか。 / How an actor is involved in the consent considerations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
+    <t>http://hl7.org/fhir/ValueSet/security-role-type|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.actor.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|Group|CareTeam|Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
+    <t xml:space="preserve">Reference(Device|4.0.1|Group|4.0.1|CareTeam|4.0.1|Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1127,7 +1127,7 @@
     <t>同意措置の詳細なコード。 / Detailed codes for the consent action.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-action</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-action|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.securityLabel</t>
@@ -1160,7 +1160,7 @@
     <t>この例外によって制御される使用目的。複数のラベルが指定されている場合、操作にはすべての指定されたラベルが必要です。 / What purposes of use are controlled by this exception. If more than one label is specified, operations must have all the specified labels.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-PurposeOfUse</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-PurposeOfUse|3.1.0</t>
   </si>
   <si>
     <t>Consent.provision.class</t>
@@ -1178,7 +1178,7 @@
     <t>同意ルールがカバーする情報のクラス（タイプ）。 / The class (type) of information a consent rule covers.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-content-class</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-class|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.code</t>
@@ -1196,7 +1196,7 @@
     <t>このコードがインスタンスで見つかった場合、例外が適用されます。 / If this code is found in an instance, then the exception applies.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-content-code</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-code|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.dataPeriod</t>
@@ -1250,7 +1250,7 @@
     <t>Consent.provision.data.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1596,7 +1596,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="80.7890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="117.01953125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1611,7 +1611,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="163.27734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.0703125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.39453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-consent.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-consent.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Consent|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Consent</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -446,7 +446,7 @@
     <t>Consent.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
@@ -484,7 +484,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -542,7 +542,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -718,7 +718,7 @@
     <t>同意リソースの4つの予想される使用。 / The four anticipated uses for the Consent Resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-scope|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-scope</t>
   </si>
   <si>
     <t>Consent.category</t>
@@ -733,7 +733,7 @@
     <t>同意声明で見つかった同意のタイプの分類。 / A classification of the type of consents found in a consent statement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-category</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -751,7 +751,7 @@
     <t>Consent.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1)
+    <t xml:space="preserve">Reference(Patient)
 </t>
   </si>
   <si>
@@ -808,7 +808,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
 </t>
   </si>
   <si>
@@ -837,7 +837,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -854,7 +854,7 @@
   </si>
   <si>
     <t>Attachment
-Reference(Consent|4.0.1|DocumentReference|4.0.1|Contract|4.0.1|QuestionnaireResponse|4.0.1)</t>
+Reference(Consent|DocumentReference|Contract|QuestionnaireResponse)</t>
   </si>
   <si>
     <t>この同意が得られる情報源 / Source from which this consent is taken</t>
@@ -955,7 +955,7 @@
     <t>規制政策の例。 / Regulatory policy examples.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-policy|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-policy</t>
   </si>
   <si>
     <t>Consent.verification</t>
@@ -992,7 +992,7 @@
     <t>Consent.verification.verifiedWith</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1090,13 +1090,13 @@
     <t>同意書対象者が同意の考慮事項にどのように関与しているか。 / How an actor is involved in the consent considerations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-role-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
   </si>
   <si>
     <t>Consent.provision.actor.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|Group|4.0.1|CareTeam|4.0.1|Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(Device|Group|CareTeam|Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
 </t>
   </si>
   <si>
@@ -1127,7 +1127,7 @@
     <t>同意措置の詳細なコード。 / Detailed codes for the consent action.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-action|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-action</t>
   </si>
   <si>
     <t>Consent.provision.securityLabel</t>
@@ -1160,7 +1160,7 @@
     <t>この例外によって制御される使用目的。複数のラベルが指定されている場合、操作にはすべての指定されたラベルが必要です。 / What purposes of use are controlled by this exception. If more than one label is specified, operations must have all the specified labels.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-PurposeOfUse|3.1.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-PurposeOfUse</t>
   </si>
   <si>
     <t>Consent.provision.class</t>
@@ -1178,7 +1178,7 @@
     <t>同意ルールがカバーする情報のクラス（タイプ）。 / The class (type) of information a consent rule covers.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-content-class|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-class</t>
   </si>
   <si>
     <t>Consent.provision.code</t>
@@ -1196,7 +1196,7 @@
     <t>このコードがインスタンスで見つかった場合、例外が適用されます。 / If this code is found in an instance, then the exception applies.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-content-code|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-code</t>
   </si>
   <si>
     <t>Consent.provision.dataPeriod</t>
@@ -1250,7 +1250,7 @@
     <t>Consent.provision.data.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1596,7 +1596,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="117.01953125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="80.7890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1611,7 +1611,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="163.27734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.39453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="45.0703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>
